--- a/보고서/일산서구.xlsx
+++ b/보고서/일산서구.xlsx
@@ -26,7 +26,7 @@
     <t>데이터 기준일자</t>
   </si>
   <si>
-    <t>2026-06-14</t>
+    <t>2026-06-21</t>
   </si>
   <si>
     <t xml:space="preserve">캠페인 정보 </t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">총 조회수 </t>
   </si>
   <si>
-    <t>337 (pv)</t>
+    <t>418 (pv)</t>
   </si>
   <si>
     <t xml:space="preserve">30일간 누적 조회수 </t>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>비율(%)</t>
+  </si>
+  <si>
+    <t>이투스247일산서구</t>
   </si>
   <si>
     <t>일산 기숙학원</t>
@@ -107,10 +110,7 @@
     <t>관리형 독서실 일산</t>
   </si>
   <si>
-    <t>이투스 설명회 후기</t>
-  </si>
-  <si>
-    <t>이투스247 주엽점</t>
+    <t>넓고 괘적한 관리형 독서실 일산</t>
   </si>
   <si>
     <t>신청자 통계</t>
@@ -206,7 +206,7 @@
     <t>일별 콘텐츠 조회수</t>
   </si>
   <si>
-    <t>날짜(2026.03.15~2026.06.14)</t>
+    <t>날짜(2026.03.22~2026.06.21)</t>
   </si>
   <si>
     <t>요일</t>
@@ -224,40 +224,61 @@
     <t>일</t>
   </si>
   <si>
-    <t>2026-06-13</t>
+    <t>2026-06-20</t>
   </si>
   <si>
     <t>토</t>
   </si>
   <si>
-    <t>2026-06-12</t>
+    <t>2026-06-19</t>
   </si>
   <si>
     <t>금</t>
   </si>
   <si>
-    <t>2026-06-11</t>
+    <t>2026-06-18</t>
   </si>
   <si>
     <t>목</t>
   </si>
   <si>
-    <t>2026-06-10</t>
+    <t>2026-06-17</t>
   </si>
   <si>
     <t>수</t>
   </si>
   <si>
-    <t>2026-06-09</t>
+    <t>2026-06-16</t>
   </si>
   <si>
     <t>화</t>
   </si>
   <si>
-    <t>2026-06-08</t>
+    <t>2026-06-15</t>
   </si>
   <si>
     <t>월</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>2026-06-09</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
   </si>
   <si>
     <t>2026-06-07</t>
@@ -494,27 +515,6 @@
     <t>2026-03-22</t>
   </si>
   <si>
-    <t>2026-03-21</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>2026-03-19</t>
-  </si>
-  <si>
-    <t>2026-03-18</t>
-  </si>
-  <si>
-    <t>2026-03-17</t>
-  </si>
-  <si>
-    <t>2026-03-16</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
     <t>콘텐츠 목록</t>
   </si>
   <si>
@@ -572,13 +572,13 @@
     <t>총합</t>
   </si>
   <si>
+    <t>이투스247학원 일산서구점</t>
+  </si>
+  <si>
     <t>주엽역 재수</t>
   </si>
   <si>
     <t>247공부환경</t>
-  </si>
-  <si>
-    <t>이투스247학원 일산서구점</t>
   </si>
   <si>
     <t>247시스템</t>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="E20" s="43"/>
       <c r="F20" s="43">
-        <v>0.16666666666667</v>
+        <v>0.21428571428571</v>
       </c>
       <c r="G20" s="24"/>
     </row>
@@ -1920,7 +1920,7 @@
       <c r="D21" s="27"/>
       <c r="E21" s="46"/>
       <c r="F21" s="46">
-        <v>0.16666666666667</v>
+        <v>0.14285714285714</v>
       </c>
       <c r="G21" s="24"/>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="E22" s="43"/>
       <c r="F22" s="43">
-        <v>0.083333333333333</v>
+        <v>0.14285714285714</v>
       </c>
       <c r="G22" s="24"/>
     </row>
@@ -1949,7 +1949,7 @@
       <c r="D23" s="27"/>
       <c r="E23" s="46"/>
       <c r="F23" s="46">
-        <v>0.083333333333333</v>
+        <v>0.071428571428571</v>
       </c>
       <c r="G23" s="24"/>
     </row>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="E24" s="43"/>
       <c r="F24" s="43">
-        <v>0.083333333333333</v>
+        <v>0.071428571428571</v>
       </c>
       <c r="G24" s="24"/>
     </row>
@@ -1978,7 +1978,7 @@
       <c r="D25" s="27"/>
       <c r="E25" s="46"/>
       <c r="F25" s="46">
-        <v>0.083333333333333</v>
+        <v>0.071428571428571</v>
       </c>
       <c r="G25" s="24"/>
     </row>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="E26" s="43"/>
       <c r="F26" s="43">
-        <v>0.083333333333333</v>
+        <v>0.071428571428571</v>
       </c>
       <c r="G26" s="24"/>
     </row>
@@ -2007,7 +2007,7 @@
       <c r="D27" s="27"/>
       <c r="E27" s="46"/>
       <c r="F27" s="46">
-        <v>0.083333333333333</v>
+        <v>0.071428571428571</v>
       </c>
       <c r="G27" s="24"/>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="E28" s="43"/>
       <c r="F28" s="43">
-        <v>0.083333333333333</v>
+        <v>0.071428571428571</v>
       </c>
       <c r="G28" s="24"/>
     </row>
@@ -2036,7 +2036,7 @@
       <c r="D29" s="37"/>
       <c r="E29" s="49"/>
       <c r="F29" s="49">
-        <v>0.083333333333333</v>
+        <v>0.071428571428571</v>
       </c>
       <c r="G29" s="24"/>
     </row>
@@ -3411,13 +3411,13 @@
         <v>67</v>
       </c>
       <c r="E3" s="82">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" s="82">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G3" s="82">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Z3" s="83"/>
     </row>
@@ -3434,10 +3434,10 @@
         <v>5</v>
       </c>
       <c r="F4" s="86">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G4" s="86">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="Z4" s="83"/>
     </row>
@@ -3451,13 +3451,13 @@
         <v>71</v>
       </c>
       <c r="E5" s="82">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="82">
         <v>4</v>
       </c>
       <c r="G5" s="82">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z5" s="83"/>
     </row>
@@ -3471,13 +3471,13 @@
         <v>73</v>
       </c>
       <c r="E6" s="86">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F6" s="86">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G6" s="86">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z6" s="83"/>
     </row>
@@ -3494,10 +3494,10 @@
         <v>7</v>
       </c>
       <c r="F7" s="82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="82">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z7" s="83"/>
     </row>
@@ -3511,10 +3511,10 @@
         <v>77</v>
       </c>
       <c r="E8" s="86">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F8" s="86">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G8" s="86">
         <v>13</v>
@@ -3534,10 +3534,10 @@
         <v>6</v>
       </c>
       <c r="F9" s="82">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G9" s="82">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Z9" s="83"/>
     </row>
@@ -3551,13 +3551,13 @@
         <v>67</v>
       </c>
       <c r="E10" s="86">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F10" s="86">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G10" s="86">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z10" s="83"/>
     </row>
@@ -3571,13 +3571,13 @@
         <v>69</v>
       </c>
       <c r="E11" s="82">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F11" s="82">
+        <v>2</v>
+      </c>
+      <c r="G11" s="82">
         <v>7</v>
-      </c>
-      <c r="G11" s="82">
-        <v>18</v>
       </c>
       <c r="Z11" s="83"/>
     </row>
@@ -3591,13 +3591,13 @@
         <v>71</v>
       </c>
       <c r="E12" s="86">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F12" s="86">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G12" s="86">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="Z12" s="83"/>
     </row>
@@ -3611,13 +3611,13 @@
         <v>73</v>
       </c>
       <c r="E13" s="82">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="F13" s="82">
-        <v>93</v>
+        <v>11</v>
       </c>
       <c r="G13" s="82">
-        <v>189</v>
+        <v>12</v>
       </c>
       <c r="Z13" s="83"/>
     </row>
@@ -3631,13 +3631,13 @@
         <v>75</v>
       </c>
       <c r="E14" s="86">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F14" s="86">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G14" s="86">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="Z14" s="83"/>
     </row>
@@ -3651,13 +3651,13 @@
         <v>77</v>
       </c>
       <c r="E15" s="82">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F15" s="82">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G15" s="82">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z15" s="83"/>
     </row>
@@ -3671,13 +3671,13 @@
         <v>79</v>
       </c>
       <c r="E16" s="86">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F16" s="86">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G16" s="86">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z16" s="83"/>
     </row>
@@ -3691,13 +3691,13 @@
         <v>67</v>
       </c>
       <c r="E17" s="82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F17" s="82">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G17" s="82">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z17" s="83"/>
     </row>
@@ -3711,13 +3711,13 @@
         <v>69</v>
       </c>
       <c r="E18" s="86">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F18" s="86">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G18" s="86">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z18" s="83"/>
     </row>
@@ -3731,13 +3731,13 @@
         <v>71</v>
       </c>
       <c r="E19" s="82">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F19" s="82">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G19" s="82">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z19" s="83"/>
     </row>
@@ -3751,13 +3751,13 @@
         <v>73</v>
       </c>
       <c r="E20" s="86">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="F20" s="86">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="G20" s="86">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="Z20" s="83"/>
     </row>
@@ -3771,13 +3771,13 @@
         <v>75</v>
       </c>
       <c r="E21" s="82">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F21" s="82">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G21" s="82">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Z21" s="83"/>
     </row>
@@ -13559,7 +13559,7 @@
         <v>172</v>
       </c>
       <c r="D3" s="94" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E3" s="24">
         <v>164</v>
@@ -13593,7 +13593,7 @@
         <v>175</v>
       </c>
       <c r="D5" s="99" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E5" s="98">
         <v>22</v>
@@ -13627,7 +13627,7 @@
         <v>178</v>
       </c>
       <c r="D7" s="94" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E7" s="24">
         <v>4</v>
@@ -23765,26 +23765,26 @@
         <v>0</v>
       </c>
       <c r="Q4" s="113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" s="113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" s="113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" s="113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" s="113">
         <v>0</v>
       </c>
       <c r="V4" s="113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" s="113">
         <f>SUM(B4:V4)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z4"/>
     </row>
@@ -23850,14 +23850,14 @@
         <v>1</v>
       </c>
       <c r="U5" s="115">
+        <v>0</v>
+      </c>
+      <c r="V5" s="115">
         <v>1</v>
-      </c>
-      <c r="V5" s="115">
-        <v>2</v>
       </c>
       <c r="W5" s="113">
         <f>SUM(B5:V5)</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z5"/>
     </row>
@@ -23911,26 +23911,26 @@
         <v>0</v>
       </c>
       <c r="Q6" s="113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" s="113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" s="113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" s="113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="113">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W6" s="113">
         <f>SUM(B6:V6)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z6"/>
     </row>

--- a/보고서/일산서구.xlsx
+++ b/보고서/일산서구.xlsx
@@ -26,7 +26,7 @@
     <t>데이터 기준일자</t>
   </si>
   <si>
-    <t>2026-06-21</t>
+    <t>2026-08-18</t>
   </si>
   <si>
     <t xml:space="preserve">캠페인 정보 </t>
@@ -59,16 +59,19 @@
     <t xml:space="preserve">총 조회수 </t>
   </si>
   <si>
-    <t>418 (pv)</t>
+    <t>712 (pv)</t>
   </si>
   <si>
     <t xml:space="preserve">30일간 누적 조회수 </t>
   </si>
   <si>
+    <t>52 (pv)</t>
+  </si>
+  <si>
     <t xml:space="preserve">일일 평균 조회수 </t>
   </si>
   <si>
-    <t>13 (pv)</t>
+    <t>8 (pv)</t>
   </si>
   <si>
     <t>유입 키워드 TOP 10</t>
@@ -83,6 +86,9 @@
     <t>비율(%)</t>
   </si>
   <si>
+    <t>이투스247 일산서구</t>
+  </si>
+  <si>
     <t>이투스247일산서구</t>
   </si>
   <si>
@@ -92,25 +98,22 @@
     <t>일산독학재수학원</t>
   </si>
   <si>
+    <t>관리형 독서실 일산</t>
+  </si>
+  <si>
     <t>031-907-0247</t>
   </si>
   <si>
     <t>이투스247일산</t>
   </si>
   <si>
+    <t>일산 이투스재수학원</t>
+  </si>
+  <si>
     <t>후곡 재수독학학원</t>
   </si>
   <si>
-    <t>화정 맛집</t>
-  </si>
-  <si>
-    <t>고등학생 관리형독서실</t>
-  </si>
-  <si>
-    <t>관리형 독서실 일산</t>
-  </si>
-  <si>
-    <t>넓고 괘적한 관리형 독서실 일산</t>
+    <t>일산독학재수</t>
   </si>
   <si>
     <t>신청자 통계</t>
@@ -173,7 +176,7 @@
     <t>경기</t>
   </si>
   <si>
-    <t>24명</t>
+    <t>25명</t>
   </si>
   <si>
     <t>서울</t>
@@ -183,9 +186,6 @@
   </si>
   <si>
     <t>기타</t>
-  </si>
-  <si>
-    <t>5명</t>
   </si>
   <si>
     <t>인천</t>
@@ -206,7 +206,7 @@
     <t>일별 콘텐츠 조회수</t>
   </si>
   <si>
-    <t>날짜(2026.03.22~2026.06.21)</t>
+    <t>날짜(2026.05.19~2026.08.18)</t>
   </si>
   <si>
     <t>요일</t>
@@ -221,43 +221,217 @@
     <t>합산 조회수(PC+Mobile)</t>
   </si>
   <si>
+    <t>화</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>월</t>
+  </si>
+  <si>
+    <t>2026-08-16</t>
+  </si>
+  <si>
     <t>일</t>
+  </si>
+  <si>
+    <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>토</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>금</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>목</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>수</t>
+  </si>
+  <si>
+    <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>2026-08-09</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>2026-08-02</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-26</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-19</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-07-12</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-05</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-07-02</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>2026-06-23</t>
+  </si>
+  <si>
+    <t>2026-06-22</t>
+  </si>
+  <si>
+    <t>2026-06-21</t>
   </si>
   <si>
     <t>2026-06-20</t>
   </si>
   <si>
-    <t>토</t>
-  </si>
-  <si>
     <t>2026-06-19</t>
-  </si>
-  <si>
-    <t>금</t>
   </si>
   <si>
     <t>2026-06-18</t>
   </si>
   <si>
-    <t>목</t>
-  </si>
-  <si>
     <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>수</t>
   </si>
   <si>
     <t>2026-06-16</t>
   </si>
   <si>
-    <t>화</t>
-  </si>
-  <si>
     <t>2026-06-15</t>
-  </si>
-  <si>
-    <t>월</t>
   </si>
   <si>
     <t>2026-06-14</t>
@@ -339,180 +513,6 @@
   </si>
   <si>
     <t>2026-05-19</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>2026-05-16</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>2026-05-14</t>
-  </si>
-  <si>
-    <t>2026-05-13</t>
-  </si>
-  <si>
-    <t>2026-05-12</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>2026-05-10</t>
-  </si>
-  <si>
-    <t>2026-05-09</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-05-05</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>2026-05-03</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-04-28</t>
-  </si>
-  <si>
-    <t>2026-04-27</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-04-22</t>
-  </si>
-  <si>
-    <t>2026-04-21</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>2026-04-19</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>2026-04-17</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-04-15</t>
-  </si>
-  <si>
-    <t>2026-04-14</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>2026-04-12</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-04-06</t>
-  </si>
-  <si>
-    <t>2026-04-05</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>2026-04-01</t>
-  </si>
-  <si>
-    <t>2026-03-31</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>2026-03-28</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>2026-03-26</t>
-  </si>
-  <si>
-    <t>2026-03-25</t>
-  </si>
-  <si>
-    <t>2026-03-24</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2026-03-22</t>
   </si>
   <si>
     <t>콘텐츠 목록</t>
@@ -1840,7 +1840,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D15" s="33"/>
       <c r="E15" s="33"/>
@@ -1850,10 +1850,10 @@
     <row r="16" spans="1:26" customHeight="1" ht="15">
       <c r="A16" s="3"/>
       <c r="B16" s="21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D16" s="36"/>
       <c r="E16" s="36"/>
@@ -1872,7 +1872,7 @@
     <row r="18" spans="1:26" customHeight="1" ht="19.5">
       <c r="A18" s="24"/>
       <c r="B18" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" s="26"/>
       <c r="D18" s="26"/>
@@ -1883,15 +1883,15 @@
     <row r="19" spans="1:26" customHeight="1" ht="15">
       <c r="A19" s="24"/>
       <c r="B19" s="38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D19" s="40"/>
       <c r="E19" s="38"/>
       <c r="F19" s="38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G19" s="24"/>
     </row>
@@ -1901,11 +1901,11 @@
         <v>1</v>
       </c>
       <c r="C20" s="42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E20" s="43"/>
       <c r="F20" s="43">
-        <v>0.21428571428571</v>
+        <v>0.26315789473684</v>
       </c>
       <c r="G20" s="24"/>
     </row>
@@ -1915,12 +1915,12 @@
         <v>2</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D21" s="27"/>
       <c r="E21" s="46"/>
       <c r="F21" s="46">
-        <v>0.14285714285714</v>
+        <v>0.15789473684211</v>
       </c>
       <c r="G21" s="24"/>
     </row>
@@ -1930,11 +1930,11 @@
         <v>3</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E22" s="43"/>
       <c r="F22" s="43">
-        <v>0.14285714285714</v>
+        <v>0.10526315789474</v>
       </c>
       <c r="G22" s="24"/>
     </row>
@@ -1944,12 +1944,12 @@
         <v>4</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D23" s="27"/>
       <c r="E23" s="46"/>
       <c r="F23" s="46">
-        <v>0.071428571428571</v>
+        <v>0.10526315789474</v>
       </c>
       <c r="G23" s="24"/>
     </row>
@@ -1959,11 +1959,11 @@
         <v>5</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E24" s="43"/>
       <c r="F24" s="43">
-        <v>0.071428571428571</v>
+        <v>0.10526315789474</v>
       </c>
       <c r="G24" s="24"/>
     </row>
@@ -1973,12 +1973,12 @@
         <v>6</v>
       </c>
       <c r="C25" s="45" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D25" s="27"/>
       <c r="E25" s="46"/>
       <c r="F25" s="46">
-        <v>0.071428571428571</v>
+        <v>0.052631578947368</v>
       </c>
       <c r="G25" s="24"/>
     </row>
@@ -1988,11 +1988,11 @@
         <v>7</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E26" s="43"/>
       <c r="F26" s="43">
-        <v>0.071428571428571</v>
+        <v>0.052631578947368</v>
       </c>
       <c r="G26" s="24"/>
     </row>
@@ -2002,12 +2002,12 @@
         <v>8</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D27" s="27"/>
       <c r="E27" s="46"/>
       <c r="F27" s="46">
-        <v>0.071428571428571</v>
+        <v>0.052631578947368</v>
       </c>
       <c r="G27" s="24"/>
     </row>
@@ -2017,11 +2017,11 @@
         <v>9</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E28" s="43"/>
       <c r="F28" s="43">
-        <v>0.071428571428571</v>
+        <v>0.052631578947368</v>
       </c>
       <c r="G28" s="24"/>
     </row>
@@ -2031,12 +2031,12 @@
         <v>10</v>
       </c>
       <c r="C29" s="48" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D29" s="37"/>
       <c r="E29" s="49"/>
       <c r="F29" s="49">
-        <v>0.071428571428571</v>
+        <v>0.052631578947368</v>
       </c>
       <c r="G29" s="24"/>
     </row>
@@ -2052,7 +2052,7 @@
     <row r="31" spans="1:26" customHeight="1" ht="19.5">
       <c r="A31" s="24"/>
       <c r="B31" s="25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C31" s="26"/>
       <c r="D31" s="26"/>
@@ -2063,34 +2063,34 @@
     <row r="32" spans="1:26" customHeight="1" ht="15">
       <c r="A32" s="3"/>
       <c r="B32" s="50" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C32" s="50" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D32" s="51" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E32" s="40"/>
       <c r="F32" s="50" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G32" s="3"/>
     </row>
     <row r="33" spans="1:26" customHeight="1" ht="15">
       <c r="A33" s="52"/>
       <c r="B33" s="53" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C33" s="54" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D33" s="55">
         <v>0.825</v>
       </c>
       <c r="E33" s="27"/>
       <c r="F33" s="54" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G33" s="52"/>
     </row>
@@ -2098,30 +2098,30 @@
       <c r="A34" s="52"/>
       <c r="B34" s="56"/>
       <c r="C34" s="57" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D34" s="58">
         <v>0.175</v>
       </c>
       <c r="E34" s="59"/>
       <c r="F34" s="57" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G34" s="52"/>
     </row>
     <row r="35" spans="1:26" customHeight="1" ht="15">
       <c r="A35" s="52"/>
       <c r="B35" s="60" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C35" s="54" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D35" s="61">
         <v>0.5</v>
       </c>
       <c r="F35" s="54" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G35" s="52"/>
     </row>
@@ -2129,14 +2129,14 @@
       <c r="A36" s="52"/>
       <c r="B36" s="62"/>
       <c r="C36" s="44" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D36" s="63">
         <v>0.35</v>
       </c>
       <c r="E36" s="27"/>
       <c r="F36" s="44" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G36" s="52"/>
     </row>
@@ -2144,13 +2144,13 @@
       <c r="A37" s="52"/>
       <c r="B37" s="62"/>
       <c r="C37" s="54" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D37" s="61">
         <v>0.1</v>
       </c>
       <c r="F37" s="54" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G37" s="52"/>
     </row>
@@ -2158,30 +2158,30 @@
       <c r="A38" s="52"/>
       <c r="B38" s="64"/>
       <c r="C38" s="65" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D38" s="66">
         <v>0.05</v>
       </c>
       <c r="E38" s="34"/>
       <c r="F38" s="65" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G38" s="52"/>
     </row>
     <row r="39" spans="1:26" customHeight="1" ht="15">
       <c r="A39" s="52"/>
       <c r="B39" s="67" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C39" s="54" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D39" s="61">
-        <v>0.6</v>
+        <v>0.625</v>
       </c>
       <c r="F39" s="54" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G39" s="52"/>
     </row>
@@ -2189,14 +2189,14 @@
       <c r="A40" s="52"/>
       <c r="B40" s="62"/>
       <c r="C40" s="44" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D40" s="63">
         <v>0.2</v>
       </c>
       <c r="E40" s="27"/>
       <c r="F40" s="44" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G40" s="52"/>
     </row>
@@ -2204,13 +2204,13 @@
       <c r="A41" s="52"/>
       <c r="B41" s="62"/>
       <c r="C41" s="54" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D41" s="61">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="F41" s="54" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="G41" s="52"/>
     </row>
@@ -3411,13 +3411,13 @@
         <v>67</v>
       </c>
       <c r="E3" s="82">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F3" s="82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3" s="82">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Z3" s="83"/>
     </row>
@@ -3431,13 +3431,13 @@
         <v>69</v>
       </c>
       <c r="E4" s="86">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F4" s="86">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G4" s="86">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Z4" s="83"/>
     </row>
@@ -3451,13 +3451,13 @@
         <v>71</v>
       </c>
       <c r="E5" s="82">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F5" s="82">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" s="82">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z5" s="83"/>
     </row>
@@ -3471,13 +3471,13 @@
         <v>73</v>
       </c>
       <c r="E6" s="86">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F6" s="86">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G6" s="86">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Z6" s="83"/>
     </row>
@@ -3491,13 +3491,13 @@
         <v>75</v>
       </c>
       <c r="E7" s="82">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F7" s="82">
         <v>3</v>
       </c>
       <c r="G7" s="82">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z7" s="83"/>
     </row>
@@ -3511,13 +3511,13 @@
         <v>77</v>
       </c>
       <c r="E8" s="86">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F8" s="86">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G8" s="86">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="83"/>
     </row>
@@ -3531,13 +3531,13 @@
         <v>79</v>
       </c>
       <c r="E9" s="82">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F9" s="82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" s="82">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Z9" s="83"/>
     </row>
@@ -3551,13 +3551,13 @@
         <v>67</v>
       </c>
       <c r="E10" s="86">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F10" s="86">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G10" s="86">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Z10" s="83"/>
     </row>
@@ -3571,13 +3571,13 @@
         <v>69</v>
       </c>
       <c r="E11" s="82">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F11" s="82">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" s="82">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="83"/>
     </row>
@@ -3591,13 +3591,13 @@
         <v>71</v>
       </c>
       <c r="E12" s="86">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F12" s="86">
         <v>4</v>
       </c>
       <c r="G12" s="86">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z12" s="83"/>
     </row>
@@ -3611,13 +3611,13 @@
         <v>73</v>
       </c>
       <c r="E13" s="82">
+        <v>0</v>
+      </c>
+      <c r="F13" s="82">
         <v>1</v>
       </c>
-      <c r="F13" s="82">
-        <v>11</v>
-      </c>
       <c r="G13" s="82">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Z13" s="83"/>
     </row>
@@ -3631,13 +3631,13 @@
         <v>75</v>
       </c>
       <c r="E14" s="86">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F14" s="86">
         <v>2</v>
       </c>
       <c r="G14" s="86">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z14" s="83"/>
     </row>
@@ -3651,13 +3651,13 @@
         <v>77</v>
       </c>
       <c r="E15" s="82">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F15" s="82">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G15" s="82">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="83"/>
     </row>
@@ -3671,13 +3671,13 @@
         <v>79</v>
       </c>
       <c r="E16" s="86">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F16" s="86">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G16" s="86">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z16" s="83"/>
     </row>
@@ -3691,13 +3691,13 @@
         <v>67</v>
       </c>
       <c r="E17" s="82">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F17" s="82">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G17" s="82">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="83"/>
     </row>
@@ -3711,13 +3711,13 @@
         <v>69</v>
       </c>
       <c r="E18" s="86">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F18" s="86">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G18" s="86">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="Z18" s="83"/>
     </row>
@@ -3731,13 +3731,13 @@
         <v>71</v>
       </c>
       <c r="E19" s="82">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F19" s="82">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G19" s="82">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="Z19" s="83"/>
     </row>
@@ -3751,13 +3751,13 @@
         <v>73</v>
       </c>
       <c r="E20" s="86">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="F20" s="86">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="G20" s="86">
-        <v>189</v>
+        <v>1</v>
       </c>
       <c r="Z20" s="83"/>
     </row>
@@ -3771,13 +3771,13 @@
         <v>75</v>
       </c>
       <c r="E21" s="82">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F21" s="82">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G21" s="82">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="Z21" s="83"/>
     </row>
@@ -3794,10 +3794,10 @@
         <v>0</v>
       </c>
       <c r="F22" s="86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G22" s="86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z22" s="83"/>
     </row>
@@ -3811,13 +3811,13 @@
         <v>79</v>
       </c>
       <c r="E23" s="82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="82">
         <v>0</v>
       </c>
       <c r="G23" s="82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z23" s="83"/>
     </row>
@@ -3831,13 +3831,13 @@
         <v>67</v>
       </c>
       <c r="E24" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F24" s="86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="86">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z24" s="83"/>
     </row>
@@ -3854,10 +3854,10 @@
         <v>0</v>
       </c>
       <c r="F25" s="82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z25" s="83"/>
     </row>
@@ -3894,10 +3894,10 @@
         <v>0</v>
       </c>
       <c r="F27" s="82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z27" s="83"/>
     </row>
@@ -3954,10 +3954,10 @@
         <v>0</v>
       </c>
       <c r="F30" s="86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" s="86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z30" s="83"/>
     </row>
@@ -3971,13 +3971,13 @@
         <v>67</v>
       </c>
       <c r="E31" s="82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G31" s="82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z31" s="83"/>
     </row>
@@ -3994,10 +3994,10 @@
         <v>0</v>
       </c>
       <c r="F32" s="86">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G32" s="86">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z32" s="83"/>
     </row>
@@ -4011,13 +4011,13 @@
         <v>71</v>
       </c>
       <c r="E33" s="82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G33" s="82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z33" s="83"/>
     </row>
@@ -4031,13 +4031,13 @@
         <v>73</v>
       </c>
       <c r="E34" s="86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G34" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z34" s="83"/>
     </row>
@@ -4054,10 +4054,10 @@
         <v>0</v>
       </c>
       <c r="F35" s="82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G35" s="82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z35" s="83"/>
     </row>
@@ -4071,13 +4071,13 @@
         <v>77</v>
       </c>
       <c r="E36" s="86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="86">
         <v>0</v>
       </c>
       <c r="G36" s="86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z36" s="83"/>
     </row>
@@ -4091,13 +4091,13 @@
         <v>79</v>
       </c>
       <c r="E37" s="82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F37" s="82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G37" s="82">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z37" s="83"/>
     </row>
@@ -4111,13 +4111,13 @@
         <v>67</v>
       </c>
       <c r="E38" s="86">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F38" s="86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G38" s="86">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z38" s="83"/>
     </row>
@@ -4131,13 +4131,13 @@
         <v>69</v>
       </c>
       <c r="E39" s="82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F39" s="82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G39" s="82">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z39" s="83"/>
     </row>
@@ -4151,13 +4151,13 @@
         <v>71</v>
       </c>
       <c r="E40" s="86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F40" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G40" s="86">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z40" s="83"/>
     </row>
@@ -4171,13 +4171,13 @@
         <v>73</v>
       </c>
       <c r="E41" s="82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F41" s="82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" s="82">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z41" s="83"/>
     </row>
@@ -4191,13 +4191,13 @@
         <v>75</v>
       </c>
       <c r="E42" s="86">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F42" s="86">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G42" s="86">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z42" s="83"/>
     </row>
@@ -4211,13 +4211,13 @@
         <v>77</v>
       </c>
       <c r="E43" s="82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F43" s="82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" s="82">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z43" s="83"/>
     </row>
@@ -4231,13 +4231,13 @@
         <v>79</v>
       </c>
       <c r="E44" s="86">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F44" s="86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G44" s="86">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z44" s="83"/>
     </row>
@@ -4251,13 +4251,13 @@
         <v>67</v>
       </c>
       <c r="E45" s="82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="82">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G45" s="82">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z45" s="83"/>
     </row>
@@ -4271,13 +4271,13 @@
         <v>69</v>
       </c>
       <c r="E46" s="86">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F46" s="86">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G46" s="86">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z46" s="83"/>
     </row>
@@ -4291,13 +4291,13 @@
         <v>71</v>
       </c>
       <c r="E47" s="82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F47" s="82">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G47" s="82">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z47" s="83"/>
     </row>
@@ -4311,13 +4311,13 @@
         <v>73</v>
       </c>
       <c r="E48" s="86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F48" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G48" s="86">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z48" s="83"/>
     </row>
@@ -4331,13 +4331,13 @@
         <v>75</v>
       </c>
       <c r="E49" s="82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F49" s="82">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G49" s="82">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z49" s="83"/>
     </row>
@@ -4351,13 +4351,13 @@
         <v>77</v>
       </c>
       <c r="E50" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F50" s="86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G50" s="86">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z50" s="83"/>
     </row>
@@ -4371,13 +4371,13 @@
         <v>79</v>
       </c>
       <c r="E51" s="82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F51" s="82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G51" s="82">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z51" s="83"/>
     </row>
@@ -4391,13 +4391,13 @@
         <v>67</v>
       </c>
       <c r="E52" s="86">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F52" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G52" s="86">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z52" s="83"/>
     </row>
@@ -4411,13 +4411,13 @@
         <v>69</v>
       </c>
       <c r="E53" s="82">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F53" s="82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G53" s="82">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z53" s="83"/>
     </row>
@@ -4431,13 +4431,13 @@
         <v>71</v>
       </c>
       <c r="E54" s="86">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F54" s="86">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G54" s="86">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z54" s="83"/>
     </row>
@@ -4451,13 +4451,13 @@
         <v>73</v>
       </c>
       <c r="E55" s="82">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F55" s="82">
         <v>0</v>
       </c>
       <c r="G55" s="82">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z55" s="83"/>
     </row>
@@ -4471,13 +4471,13 @@
         <v>75</v>
       </c>
       <c r="E56" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F56" s="86">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G56" s="86">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z56" s="83"/>
     </row>
@@ -4491,13 +4491,13 @@
         <v>77</v>
       </c>
       <c r="E57" s="82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F57" s="82">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G57" s="82">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z57" s="83"/>
     </row>
@@ -4511,13 +4511,13 @@
         <v>79</v>
       </c>
       <c r="E58" s="86">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F58" s="86">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G58" s="86">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z58" s="83"/>
     </row>
@@ -4531,13 +4531,13 @@
         <v>67</v>
       </c>
       <c r="E59" s="82">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F59" s="82">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G59" s="82">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z59" s="83"/>
     </row>
@@ -4551,13 +4551,13 @@
         <v>69</v>
       </c>
       <c r="E60" s="86">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F60" s="86">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G60" s="86">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z60" s="83"/>
     </row>
@@ -4571,13 +4571,13 @@
         <v>71</v>
       </c>
       <c r="E61" s="82">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F61" s="82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G61" s="82">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z61" s="83"/>
     </row>
@@ -4591,13 +4591,13 @@
         <v>73</v>
       </c>
       <c r="E62" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F62" s="86">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G62" s="86">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z62" s="83"/>
     </row>
@@ -4611,13 +4611,13 @@
         <v>75</v>
       </c>
       <c r="E63" s="82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F63" s="82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G63" s="82">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z63" s="83"/>
     </row>
@@ -4631,13 +4631,13 @@
         <v>77</v>
       </c>
       <c r="E64" s="86">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F64" s="86">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G64" s="86">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z64" s="83"/>
     </row>
@@ -4651,13 +4651,13 @@
         <v>79</v>
       </c>
       <c r="E65" s="82">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F65" s="82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G65" s="82">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z65" s="83"/>
     </row>
@@ -4671,13 +4671,13 @@
         <v>67</v>
       </c>
       <c r="E66" s="86">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F66" s="86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G66" s="86">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z66" s="83"/>
     </row>
@@ -4691,13 +4691,13 @@
         <v>69</v>
       </c>
       <c r="E67" s="82">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F67" s="82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G67" s="82">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z67" s="83"/>
     </row>
@@ -4711,13 +4711,13 @@
         <v>71</v>
       </c>
       <c r="E68" s="86">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F68" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G68" s="86">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z68" s="83"/>
     </row>
@@ -4731,13 +4731,13 @@
         <v>73</v>
       </c>
       <c r="E69" s="82">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F69" s="82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G69" s="82">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z69" s="83"/>
     </row>
@@ -4751,13 +4751,13 @@
         <v>75</v>
       </c>
       <c r="E70" s="86">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F70" s="86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G70" s="86">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z70" s="83"/>
     </row>
@@ -4771,13 +4771,13 @@
         <v>77</v>
       </c>
       <c r="E71" s="82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" s="82">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G71" s="82">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z71" s="83"/>
     </row>
@@ -4791,13 +4791,13 @@
         <v>79</v>
       </c>
       <c r="E72" s="86">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F72" s="86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G72" s="86">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z72" s="83"/>
     </row>
@@ -4811,13 +4811,13 @@
         <v>67</v>
       </c>
       <c r="E73" s="82">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F73" s="82">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G73" s="82">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z73" s="83"/>
     </row>
@@ -4831,13 +4831,13 @@
         <v>69</v>
       </c>
       <c r="E74" s="86">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F74" s="86">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G74" s="86">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z74" s="83"/>
     </row>
@@ -4851,13 +4851,13 @@
         <v>71</v>
       </c>
       <c r="E75" s="82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F75" s="82">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G75" s="82">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z75" s="83"/>
     </row>
@@ -4871,13 +4871,13 @@
         <v>73</v>
       </c>
       <c r="E76" s="86">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F76" s="86">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G76" s="86">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z76" s="83"/>
     </row>
@@ -4891,13 +4891,13 @@
         <v>75</v>
       </c>
       <c r="E77" s="82">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F77" s="82">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G77" s="82">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z77" s="83"/>
     </row>
@@ -4911,13 +4911,13 @@
         <v>77</v>
       </c>
       <c r="E78" s="86">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="F78" s="86">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="G78" s="86">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="Z78" s="83"/>
     </row>
@@ -4931,13 +4931,13 @@
         <v>79</v>
       </c>
       <c r="E79" s="82">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F79" s="82">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G79" s="82">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Z79" s="83"/>
     </row>
@@ -13559,7 +13559,7 @@
         <v>172</v>
       </c>
       <c r="D3" s="94" t="s">
-        <v>91</v>
+        <v>149</v>
       </c>
       <c r="E3" s="24">
         <v>164</v>
@@ -13593,7 +13593,7 @@
         <v>175</v>
       </c>
       <c r="D5" s="99" t="s">
-        <v>91</v>
+        <v>149</v>
       </c>
       <c r="E5" s="98">
         <v>22</v>
@@ -13627,7 +13627,7 @@
         <v>178</v>
       </c>
       <c r="D7" s="94" t="s">
-        <v>91</v>
+        <v>149</v>
       </c>
       <c r="E7" s="24">
         <v>4</v>
@@ -23619,7 +23619,7 @@
     </row>
     <row r="2" spans="1:26" customHeight="1" ht="18">
       <c r="A2" s="104" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="105" t="s">
         <v>182</v>
